--- a/Document/操作方法/操作方法.xlsx
+++ b/Document/操作方法/操作方法.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\操作方法\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8997740E-C1BD-4B8B-8F70-22E4386BA72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D052639F-C002-4837-A51E-413BB25B6AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="3435" windowWidth="28170" windowHeight="14655" activeTab="4" xr2:uid="{32933362-AF1C-49DB-BDD3-B20D31F5CF48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{32933362-AF1C-49DB-BDD3-B20D31F5CF48}"/>
   </bookViews>
   <sheets>
     <sheet name="インストール手順" sheetId="1" r:id="rId1"/>
     <sheet name="起動" sheetId="2" r:id="rId2"/>
     <sheet name="初期設定" sheetId="3" r:id="rId3"/>
-    <sheet name="記録開始" sheetId="4" r:id="rId4"/>
-    <sheet name="2個以上学習する場合" sheetId="5" r:id="rId5"/>
+    <sheet name="記録開始(新規)" sheetId="4" r:id="rId4"/>
+    <sheet name="記録開始(訂正)" sheetId="7" r:id="rId5"/>
+    <sheet name="2個以上学習する場合" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,9 +43,734 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+  <si>
+    <t>ダウンロードしたInstaller.zipを解凍してください</t>
+    <rPh sb="22" eb="24">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Installer.msiをクリックします</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Installerが起動したら次へをクリックします</t>
+    <rPh sb="10" eb="12">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次へ</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デスクトップまたは、メニューにアプリが追加されればインストール完了です。</t>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閉じる</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インストール中</t>
+    <rPh sb="6" eb="7">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起動時にメッセージが表示されます</t>
+    <rPh sb="0" eb="2">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メイン画面が開きます</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定ボタンを押下します</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定画面が開きます</t>
+    <rPh sb="0" eb="4">
+      <t>セッテイガメン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参照ボタンで学習記録の出力先フォルダを指定することができます</t>
+    <rPh sb="0" eb="2">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>シュツリョクサキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期設定</t>
+    <rPh sb="0" eb="4">
+      <t>ショキセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーションをインストールします</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起動</t>
+    <rPh sb="0" eb="2">
+      <t>キドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーションを起動します</t>
+    <rPh sb="9" eb="11">
+      <t>キドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デスクトップまたはメニューからアプリケーションをダブルクリックします</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力先やユーザー名を設定したら更新ボタンを押下します。</t>
+    <rPh sb="0" eb="3">
+      <t>シュツリョクサキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はいを押下します</t>
+    <rPh sb="3" eb="5">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存されます</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録開始(新規)</t>
+  </si>
+  <si>
+    <t>学習記録の出力先フォルダなどを設定します</t>
+    <rPh sb="0" eb="4">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>シュツリョクサキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録モード[登録]で学習記録を登録します</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録モード[登録]では、今日の日付の学習記録のみ登録することができます</t>
+    <rPh sb="12" eb="14">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すでに今日の日付で登録されている場合は、登録モード[訂正]で変更できます</t>
+    <rPh sb="3" eb="5">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学習した資格名を入力し、表示ボタンを押下します</t>
+    <rPh sb="0" eb="2">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定画面で設定したフォルダに学習記録用のファイルが保存されていない場合、メッセージが表示されます。</t>
+    <rPh sb="0" eb="4">
+      <t>セッテイガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すでに作成済みの状態で表示された場合は、設定画面の出力先と保存されているファイル名を確認してください</t>
+    <rPh sb="3" eb="6">
+      <t>サクセイズ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>セッテイガメン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>シュツリョクサキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボディ部分が入力可能になります</t>
+    <rPh sb="3" eb="5">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ニュウリョクカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学習内容を入力します</t>
+    <rPh sb="0" eb="4">
+      <t>ガクシュウナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録するを押下するとメッセージが表示されるので「はい」を押下します</t>
+    <rPh sb="0" eb="2">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録が正常終了すると、ファイル名と出力したシート名が表示されます</t>
+    <rPh sb="0" eb="2">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォルダを確認します</t>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルを開くと学習内容が記録されていることを確認できます。</t>
+    <rPh sb="5" eb="6">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ガクシュウナイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録開始(訂正)</t>
+  </si>
+  <si>
+    <t>学習内容の訂正を行います</t>
+    <rPh sb="0" eb="4">
+      <t>ガクシュウナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去の日付で登録することも可能です</t>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去の日付の学習記録の登録についても同様です</t>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>昨日の学習記録を登録し忘れてしまった場合は登録モード[訂正]で登録を行ってください</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録モード[訂正]にすると学習日が変更できます</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ガクシュウビ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>訂正したい学習日を選択してください</t>
+    <rPh sb="0" eb="2">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ガクシュウビ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示ボタンを押下すると登録した学習記録が表示されます</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未登録の日付で表示を押下した場合はメッセージが表示されます</t>
+    <rPh sb="0" eb="3">
+      <t>ミトウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学習内容を修正します</t>
+    <rPh sb="0" eb="4">
+      <t>ガクシュウナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録するボタンを押下し、メッセージで「はい」を押下します</t>
+    <rPh sb="0" eb="2">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>訂正された内容を確認します</t>
+    <rPh sb="0" eb="2">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2個以上学習する場合</t>
+  </si>
+  <si>
+    <t>別の試験などの学習内容を記録します</t>
+    <rPh sb="0" eb="1">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シケン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ガクシュウナイヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資格名を入力します</t>
+    <rPh sb="0" eb="2">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定画面で設定したフォルダに学習記録用のファイルが存在するが、シート自体が存在しない場合、メッセージが表示されます。</t>
+    <rPh sb="0" eb="4">
+      <t>セッテイガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すでに作成済みの状態で表示された場合は、シート名などを確認してください</t>
+    <rPh sb="3" eb="6">
+      <t>サクセイズ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シート[記録開始(新規)]と同様の操作で記録を行います</t>
+    <rPh sb="14" eb="16">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シートが追加され新たに学習記録が記録されます</t>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ガクシュウキロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,6 +783,33 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -83,8 +836,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -110,21 +872,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>439073</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>181166</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>478135</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>229961</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D873CE4A-8D01-45C4-AF08-05CED4FB350B}"/>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8354EC1C-4434-61DA-DCF6-C1A1975F575C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -140,8 +902,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1190625"/>
-          <a:ext cx="6611273" cy="1371791"/>
+          <a:off x="268941" y="34368441"/>
+          <a:ext cx="13465753" cy="9642902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -154,14 +916,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>638838</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>86269</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>86270</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -198,14 +960,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>638838</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>86269</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>86268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -242,14 +1004,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>638838</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>86269</xdr:rowOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>86268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -286,14 +1048,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>638838</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>86269</xdr:rowOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>86270</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -330,14 +1092,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>638838</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>86269</xdr:rowOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>86268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -370,69 +1132,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>384403</xdr:colOff>
-      <xdr:row>176</xdr:row>
-      <xdr:rowOff>144789</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A09B9E8-F461-8FAC-123F-988E7C704890}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="28336875"/>
-          <a:ext cx="24387403" cy="13717914"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>390524</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C77DE99-89A6-C54D-E1AA-DC17D226FC09}"/>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBDADBD-A5FD-4D71-AF89-7BCA60E2A146}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -440,8 +1158,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="704850" y="37566600"/>
-          <a:ext cx="971550" cy="1057275"/>
+          <a:off x="5924549" y="36957000"/>
+          <a:ext cx="3648075" cy="1057275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -480,25 +1198,113 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>562819</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>28744</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C61DDE6D-A483-A342-62ED-4E4D9273FFF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1190625"/>
+          <a:ext cx="6049219" cy="1219370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>861</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>153220</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A3F4B3-22DD-F044-356D-B079E7E07D37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="266700" y="952500"/>
+          <a:ext cx="6173061" cy="5868219"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>466724</xdr:colOff>
-      <xdr:row>142</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>685799</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="正方形/長方形 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBDADBD-A5FD-4D71-AF89-7BCA60E2A146}"/>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{183A50F1-64BB-46FF-9394-387C74E6807F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -506,8 +1312,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9382124" y="34023300"/>
-          <a:ext cx="3648075" cy="1057275"/>
+          <a:off x="276225" y="34823401"/>
+          <a:ext cx="971550" cy="685800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -546,6 +1352,402 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>85726</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>96372</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{652AA9C8-E3B1-43BC-B1B4-FFFC5DF677F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3088902" y="32582225"/>
+          <a:ext cx="969309" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>78441</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>364191</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>60511</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECDA8774-15D7-4293-804D-A52C6E734F89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3081617" y="22949647"/>
+          <a:ext cx="969309" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>375397</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>60511</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="正方形/長方形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAD58D99-A8E4-4CEF-9431-9FE8498ED73D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3092823" y="18007853"/>
+          <a:ext cx="969309" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>78442</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>112058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>364192</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>60510</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA795128-C83A-4E19-ADC5-A892178572A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3081618" y="13301382"/>
+          <a:ext cx="969309" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>459442</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>168088</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>116540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E21DC1C-2D9A-4D86-BC17-1F8A74D31CA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1411942" y="3697941"/>
+          <a:ext cx="3731558" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56029</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>341779</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>228599</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3CD095B-9648-46E1-A50E-C2D07A94E999}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="324970" y="7821706"/>
+          <a:ext cx="969309" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -555,13 +1757,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>124034</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -599,21 +1801,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>435553</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>117902</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAB3B396-23FA-2EDC-DDA1-CF3327EA2D7A}"/>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF03CFB-14E0-422A-A5A9-5ED84D30AF3B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -629,8 +1831,184 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="3333750"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="304800" y="800100"/>
+          <a:ext cx="13465753" cy="9642902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>293034</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29537DC2-7647-46E8-B474-F6371BED95F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="314325" y="847726"/>
+          <a:ext cx="969309" cy="723899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>445994</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7186414A-72FC-4B36-BC23-F769B2373C96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6029325" y="3705225"/>
+          <a:ext cx="3636869" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>515092</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53271DB4-9767-ED86-78B3-DD4926F437CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="304800" y="14611350"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -653,16 +2031,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:colOff>515092</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C46B2C8-07DC-49E0-A9AC-030D30201635}"/>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C8D1329-2F87-3BC4-E587-25CD4313D53B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -678,8 +2056,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1190625"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="314325" y="1276350"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -692,21 +2070,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>238828</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>190859</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552719</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82382603-2BC7-4E0A-A223-09BAEE6B307A}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AEFAB41-DDCE-ACB1-46B0-67A359A86888}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -722,8 +2100,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="7858125"/>
-          <a:ext cx="5039428" cy="2572109"/>
+          <a:off x="685800" y="14763750"/>
+          <a:ext cx="1924319" cy="1448002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -736,21 +2114,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>238828</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>190859</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>124034</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C34681CE-7BF8-5F32-C292-83C7EDD6AB22}"/>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77C3984-2A95-31AB-584D-BD54B47AF0E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -766,35 +2144,101 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="11191875"/>
-          <a:ext cx="5039428" cy="2572109"/>
+          <a:off x="685800" y="16906875"/>
+          <a:ext cx="1495634" cy="1448002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>435909</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0C10482-9485-4108-B0E1-DB091F4A2316}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="466725" y="6143625"/>
+          <a:ext cx="969309" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552719</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>19252</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>238828</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>190859</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AEFAB41-DDCE-ACB1-46B0-67A359A86888}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25438288-AA72-0882-9A2C-DD29E9BF5533}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -810,8 +2254,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="14763750"/>
-          <a:ext cx="1924319" cy="1448002"/>
+          <a:off x="314325" y="7858125"/>
+          <a:ext cx="5039428" cy="2572109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -824,21 +2268,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>124034</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>19252</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>20393</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>67482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77C3984-2A95-31AB-584D-BD54B47AF0E8}"/>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C75C07E8-ABA7-E939-3065-F388B571D0C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -854,14 +2298,224 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="16906875"/>
-          <a:ext cx="1495634" cy="1448002"/>
+          <a:off x="314325" y="10953750"/>
+          <a:ext cx="9621593" cy="5782482"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>238828</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>190859</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C268592-D85D-85DE-0595-78EC94B36144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="314325" y="17945100"/>
+          <a:ext cx="5039428" cy="2572109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>219074</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="吹き出し: 角を丸めた四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB16D7D5-0E5C-B23A-A4C3-071EC8F02EC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1009650" y="19831049"/>
+          <a:ext cx="2400300" cy="895351"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -54753"/>
+            <a:gd name="adj2" fmla="val -41207"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ここは自動出力推奨です</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>手動出力は記録するたびに出力先ファイルを指定するモードです</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B13C166-E0EC-4EB9-A1F0-8291EB5F3AF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3590925" y="20288250"/>
+          <a:ext cx="828675" cy="419099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -873,21 +2527,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276494</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E26F97F-9919-E0F4-B17E-F56FE218BDAF}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{723F5D43-5989-E34D-2AE4-733DA134A1A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -903,8 +2557,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="714375"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="685800" y="7381875"/>
+          <a:ext cx="1924319" cy="1448002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -917,21 +2571,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552719</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>19252</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238867</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{723F5D43-5989-E34D-2AE4-733DA134A1A8}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90B7F653-F268-6C60-C3B6-5DCC5D2FA8E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -947,35 +2601,167 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="7381875"/>
-          <a:ext cx="1924319" cy="1448002"/>
+          <a:off x="247650" y="714375"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A4F96D5-027F-4F68-9A0D-1811F2DEB557}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="381000" y="2400300"/>
+          <a:ext cx="1524000" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A372CBB1-7FC1-466E-8FE8-F33008CBD167}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4876800" y="2724150"/>
+          <a:ext cx="552450" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238867</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDA049FE-29D8-5A83-800F-6168FE852D58}"/>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09E888EA-159D-3F94-F065-3E16BD38420A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -991,8 +2777,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="9763125"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="247650" y="11039475"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1003,23 +2789,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238867</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4CB77D0-37FF-490A-A987-F51243586235}"/>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FD32F0D-D4E3-A4EE-F149-6E06C18C7BD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1035,35 +2821,219 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6858000" y="9763125"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="247650" y="17468850"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="吹き出し: 角を丸めた四角形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82EA9C63-2371-454F-A178-D96D646BBDFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5105400" y="19945350"/>
+          <a:ext cx="2400300" cy="685801"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -53166"/>
+            <a:gd name="adj2" fmla="val 73686"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>学習内容、備考は</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Shift+Enter</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>で改行することができます</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>219076</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="吹き出し: 角を丸めた四角形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC9F07F-00A4-4986-AAA3-A1580A7C1BA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3990975" y="22955250"/>
+          <a:ext cx="2400300" cy="685801"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -42055"/>
+            <a:gd name="adj2" fmla="val -73536"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>入力が終わったら記録するボタンを押下しましょう</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552719</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276494</xdr:colOff>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3314C95F-68B5-891B-11B5-D561BE7D48EC}"/>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B889163A-8C0E-4572-90C0-EE6DF61567A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1079,7 +3049,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="23336250"/>
+          <a:off x="247650" y="24374475"/>
           <a:ext cx="1924319" cy="1448002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1093,21 +3063,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>467269</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>162465</xdr:colOff>
+      <xdr:row>119</xdr:row>
       <xdr:rowOff>209779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12E7C9E3-08DC-B689-75E1-B0E9C1E4E368}"/>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C4284C-5BBB-F717-7817-703CD115878F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1123,8 +3093,53 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="25717500"/>
-          <a:ext cx="3896269" cy="1638529"/>
+          <a:off x="247650" y="26993850"/>
+          <a:ext cx="3867690" cy="1638529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>390526</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85636EA2-A104-8844-1894-B98E921B2B48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:srcRect r="33768" b="69148"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="247651" y="29613225"/>
+          <a:ext cx="8896350" cy="2333625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1137,21 +3152,335 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>153751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{441D9C34-7EA5-AE6E-D0F5-8EF182B5D221}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:srcRect r="44814"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="247650" y="32946975"/>
+          <a:ext cx="10020300" cy="9678751"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>219817</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD29D5A8-2723-4CA4-BFAE-961BD2E93F61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="276225" y="1990725"/>
+          <a:ext cx="5315692" cy="5439534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>219817</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17129D7F-F2F3-9A06-7E20-5E0C08394140}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="276225" y="8181975"/>
+          <a:ext cx="5315692" cy="5439534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>382585</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>366</xdr:rowOff>
+      <xdr:colOff>496039</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>210310</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BC04E23-3BAE-7D2E-CD91-25284ECD7681}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6057900" y="8420100"/>
+          <a:ext cx="5296639" cy="5449060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>219817</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59A2E858-CEB3-B75D-46AD-87101D9B51C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="276225" y="14849475"/>
+          <a:ext cx="5315692" cy="5439534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>257444</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>19252</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{497F842A-2A8C-9B6B-0152-EDF97AEF867A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="276225" y="21040725"/>
+          <a:ext cx="1924319" cy="1448002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457688</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>85936</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B63E5AB2-F70F-40D7-A490-8B37DF166030}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="276225" y="22707600"/>
+          <a:ext cx="3496163" cy="1514686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>143415</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>209779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="図 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A32D6F4-E4D4-8A4A-6C9C-DA7FB6A0E062}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9431BB2C-2370-9F5B-1376-8FD42D06D0B8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1167,8 +3496,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="28336875"/>
-          <a:ext cx="11355385" cy="2619741"/>
+          <a:off x="276225" y="24850725"/>
+          <a:ext cx="3867690" cy="1638529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1181,21 +3510,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>315750</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>153751</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2411FCAE-3737-231B-DCF5-ADB0D93570A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D557FB0-8D67-44BA-9868-F69DE5871DA6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1211,8 +3540,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="16906875"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="276225" y="27470100"/>
+          <a:ext cx="10212225" cy="9678751"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1221,74 +3550,228 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8398BCF6-C8E6-48BA-8F07-C458CDC88B54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2552699" y="2781300"/>
+          <a:ext cx="1247775" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:colOff>142874</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39ADA354-8578-4E06-B8B8-2D24EFB4347E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="419099" y="2771775"/>
+          <a:ext cx="2057401" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>438151</xdr:colOff>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>612078</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>191790</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F446E3B6-8BA6-BC73-463A-F8764888A0B8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="31670625"/>
-          <a:ext cx="17757078" cy="9240540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>552451</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{295EA185-770E-4F68-A67F-8DEF743E8187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3752851" y="19850100"/>
+          <a:ext cx="800100" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>229342</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1E8314D-8CB7-C701-53DD-0D202AC310DF}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCE9A44F-C31D-D7C8-7B7B-617AF8786994}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1304,8 +3787,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="714375"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="285750" y="1276350"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1318,21 +3801,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552719</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266969</xdr:colOff>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3CF77B5-014F-0D4B-039F-153B0237FEC6}"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61205757-8CEE-49C2-887F-726345E38E44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1348,7 +3831,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="7143750"/>
+          <a:off x="285750" y="7705725"/>
           <a:ext cx="1924319" cy="1448002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1362,21 +3845,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>612078</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>191790</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>229342</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4288728-BC89-5C98-1270-FFE6E784E447}"/>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B47400-A979-DE98-B887-A9EA2FBE012B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1392,8 +3875,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="16430625"/>
-          <a:ext cx="17757078" cy="9240540"/>
+          <a:off x="285750" y="10086975"/>
+          <a:ext cx="5315692" cy="5439534"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1406,21 +3889,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362671</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>200817</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152940</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>209779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F691450A-8DB1-8A4E-41ED-CF225167534E}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{134C006C-1EE0-65FF-4A5F-29C5FF1208A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1436,14 +3919,124 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="9525000"/>
-          <a:ext cx="5163271" cy="5677692"/>
+          <a:off x="285750" y="15801975"/>
+          <a:ext cx="3867690" cy="1638529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>315749</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>153751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CBBD6ED-FFB1-C058-D827-F403C9CF55A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285750" y="18421350"/>
+          <a:ext cx="10202699" cy="9678751"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2FFA199-22BA-4EEF-B48E-5E7E559784F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="514350" y="1666875"/>
+          <a:ext cx="1247775" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1766,20 +4359,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2631A3DA-8542-4754-8B13-A17B4D6E9868}">
-  <dimension ref="A1"/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B84" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B147" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0658B75-D6C3-45C1-BC4B-D7FFDAB85F2C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B62" s="2"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1788,9 +4471,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C39BCBCD-F348-4DC4-A62D-9EA336EFA4EB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1799,9 +4526,84 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D865BAFC-DC59-4A34-8415-25E54488D7C3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="2" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B102" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B113" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B124" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B138" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1809,10 +4611,118 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4039C6AF-765B-4200-9D44-6D1C481BF294}">
+  <dimension ref="A1:K115"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="3.625" customWidth="1"/>
+    <col min="2" max="2" width="3.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B62" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B88" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B115" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A4EA59-1E7B-4E08-865F-6DC164D15EEB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="2" width="3.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B77" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Document/操作方法/操作方法.xlsx
+++ b/Document/操作方法/操作方法.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\操作方法\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D052639F-C002-4837-A51E-413BB25B6AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAC110A-B5C3-4090-B293-C0A758C55841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{32933362-AF1C-49DB-BDD3-B20D31F5CF48}"/>
   </bookViews>
@@ -876,17 +876,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>478135</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>63833</xdr:colOff>
       <xdr:row>187</xdr:row>
-      <xdr:rowOff>229961</xdr:rowOff>
+      <xdr:rowOff>210909</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8354EC1C-4434-61DA-DCF6-C1A1975F575C}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77420018-16CE-DAAD-DB90-8969FAE9EA7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -902,8 +902,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="268941" y="34368441"/>
-          <a:ext cx="13465753" cy="9642902"/>
+          <a:off x="267891" y="35103594"/>
+          <a:ext cx="13756020" cy="9735909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1757,21 +1757,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>124034</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>19252</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>40020</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>210909</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E974B338-80CE-FB96-0E79-A566D90D17A4}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93E1B1BF-2779-CFC4-39CB-50BBD5A70F65}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1787,8 +1787,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="714375"/>
-          <a:ext cx="1495634" cy="1448002"/>
+          <a:off x="304800" y="1276350"/>
+          <a:ext cx="13756020" cy="9735909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1801,21 +1801,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>435553</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>117902</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>124034</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF03CFB-14E0-422A-A5A9-5ED84D30AF3B}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E974B338-80CE-FB96-0E79-A566D90D17A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1831,8 +1831,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304800" y="800100"/>
-          <a:ext cx="13465753" cy="9642902"/>
+          <a:off x="685800" y="714375"/>
+          <a:ext cx="1495634" cy="1448002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Document/操作方法/操作方法.xlsx
+++ b/Document/操作方法/操作方法.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\操作方法\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAC110A-B5C3-4090-B293-C0A758C55841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E2DC33-459F-4CCE-BACF-F073FD0ACD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{32933362-AF1C-49DB-BDD3-B20D31F5CF48}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>ダウンロードしたInstaller.zipを解凍してください</t>
     <rPh sb="22" eb="24">
@@ -111,16 +111,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メイン画面が開きます</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>設定ボタンを押下します</t>
     <rPh sb="0" eb="2">
       <t>セッテイ</t>
@@ -762,6 +752,53 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>.NETのランタイムがインストールされていない場合はインストールするようにメッセージが表示されます</t>
+    <rPh sb="23" eb="25">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>.NETのランタイムがインストールされている場合</t>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OKを押下するとメイン画面が開きます</t>
+    <rPh sb="3" eb="5">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「Download it now」をクリックすると公式サイトが開き、ランタイムのインストーラをダウンロードすることができます</t>
+    <rPh sb="25" eb="27">
+      <t>コウシキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダウンロードしたインストーラーをクリックしてインストールを行ってください</t>
+    <rPh sb="29" eb="30">
+      <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1801,13 +1838,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>124034</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>19252</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1977,13 +2014,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>515092</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>200784</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2013,6 +2050,115 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2049" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E627A351-CEE0-5726-64BB-37ADBB209E57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="12230100"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCACE640-E41C-472B-9F57-4752F583F631}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="12468225"/>
+          <a:ext cx="6448425" cy="2514600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4370,12 +4516,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -4428,7 +4574,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0658B75-D6C3-45C1-BC4B-D7FFDAB85F2C}">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4436,31 +4582,51 @@
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B67" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B68" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B61" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B62" s="2"/>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B79" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B80" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4479,42 +4645,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4535,72 +4701,72 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B138" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4621,55 +4787,55 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" t="s">
         <v>42</v>
-      </c>
-      <c r="K35" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -4689,37 +4855,37 @@
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
